--- a/MainTop/31.05.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/31.05.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\31.05.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A827A76-6E8C-470E-8EB2-08BECD7E7381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4A5883-BCBE-45E8-82F1-D976E0108EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,7 +546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -557,6 +557,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -879,6 +880,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -893,7 +895,7 @@
       <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="8">
         <f>B2/4</f>
         <v>37</v>
       </c>
@@ -911,7 +913,7 @@
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <f t="shared" ref="E3:E66" si="0">B3/4</f>
         <v>31</v>
       </c>
@@ -929,7 +931,7 @@
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -947,7 +949,7 @@
       <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -965,7 +967,7 @@
       <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -983,7 +985,7 @@
       <c r="D7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1001,7 +1003,7 @@
       <c r="D8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1019,7 +1021,7 @@
       <c r="D9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1037,7 +1039,7 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1055,7 +1057,7 @@
       <c r="D11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="8">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1073,7 +1075,7 @@
       <c r="D12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1091,7 +1093,7 @@
       <c r="D13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1109,7 +1111,7 @@
       <c r="D14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="8">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1127,7 +1129,7 @@
       <c r="D15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="8">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1145,7 +1147,7 @@
       <c r="D16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="8">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1163,7 +1165,7 @@
       <c r="D17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1181,7 +1183,7 @@
       <c r="D18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1199,7 +1201,7 @@
       <c r="D19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1217,7 +1219,7 @@
       <c r="D20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1235,7 +1237,7 @@
       <c r="D21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="8">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1253,7 +1255,7 @@
       <c r="D22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1271,7 +1273,7 @@
       <c r="D23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1289,7 +1291,7 @@
       <c r="D24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1307,7 +1309,7 @@
       <c r="D25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1325,7 +1327,7 @@
       <c r="D26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1343,7 +1345,7 @@
       <c r="D27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1361,7 +1363,7 @@
       <c r="D28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1379,7 +1381,7 @@
       <c r="D29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1397,7 +1399,7 @@
       <c r="D30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1415,7 +1417,7 @@
       <c r="D31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1433,7 +1435,7 @@
       <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1451,7 +1453,7 @@
       <c r="D33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1469,7 +1471,7 @@
       <c r="D34" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1487,7 +1489,7 @@
       <c r="D35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1505,7 +1507,7 @@
       <c r="D36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1523,7 +1525,7 @@
       <c r="D37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1541,7 +1543,7 @@
       <c r="D38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1559,7 +1561,7 @@
       <c r="D39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1577,7 +1579,7 @@
       <c r="D40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1595,7 +1597,7 @@
       <c r="D41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1613,7 +1615,7 @@
       <c r="D42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1631,7 +1633,7 @@
       <c r="D43" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1649,7 +1651,7 @@
       <c r="D44" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1667,7 +1669,7 @@
       <c r="D45" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1685,7 +1687,7 @@
       <c r="D46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1703,7 +1705,7 @@
       <c r="D47" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1721,7 +1723,7 @@
       <c r="D48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1739,7 +1741,7 @@
       <c r="D49" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1757,7 +1759,7 @@
       <c r="D50" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1775,7 +1777,7 @@
       <c r="D51" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1793,7 +1795,7 @@
       <c r="D52" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1811,7 +1813,7 @@
       <c r="D53" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1829,7 +1831,7 @@
       <c r="D54" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1847,7 +1849,7 @@
       <c r="D55" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1865,7 +1867,7 @@
       <c r="D56" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1883,7 +1885,7 @@
       <c r="D57" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1901,7 +1903,7 @@
       <c r="D58" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1919,7 +1921,7 @@
       <c r="D59" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1937,7 +1939,7 @@
       <c r="D60" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1955,7 +1957,7 @@
       <c r="D61" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1973,7 +1975,7 @@
       <c r="D62" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1991,7 +1993,7 @@
       <c r="D63" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2009,7 +2011,7 @@
       <c r="D64" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2027,7 +2029,7 @@
       <c r="D65" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2045,7 +2047,7 @@
       <c r="D66" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="8">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2063,7 +2065,7 @@
       <c r="D67" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="8">
         <f t="shared" ref="E67:E130" si="1">B67/4</f>
         <v>2</v>
       </c>
@@ -2081,7 +2083,7 @@
       <c r="D68" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2099,7 +2101,7 @@
       <c r="D69" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2117,7 +2119,7 @@
       <c r="D70" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2135,7 +2137,7 @@
       <c r="D71" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2153,7 +2155,7 @@
       <c r="D72" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2171,7 +2173,7 @@
       <c r="D73" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2189,7 +2191,7 @@
       <c r="D74" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2207,7 +2209,7 @@
       <c r="D75" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2225,7 +2227,7 @@
       <c r="D76" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2243,7 +2245,7 @@
       <c r="D77" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2261,7 +2263,7 @@
       <c r="D78" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2279,7 +2281,7 @@
       <c r="D79" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2297,7 +2299,7 @@
       <c r="D80" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2315,7 +2317,7 @@
       <c r="D81" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2333,7 +2335,7 @@
       <c r="D82" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2351,7 +2353,7 @@
       <c r="D83" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2369,7 +2371,7 @@
       <c r="D84" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2387,7 +2389,7 @@
       <c r="D85" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2405,7 +2407,7 @@
       <c r="D86" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2423,7 +2425,7 @@
       <c r="D87" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2441,7 +2443,7 @@
       <c r="D88" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2459,7 +2461,7 @@
       <c r="D89" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2477,7 +2479,7 @@
       <c r="D90" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2495,7 +2497,7 @@
       <c r="D91" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2513,7 +2515,7 @@
       <c r="D92" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2531,7 +2533,7 @@
       <c r="D93" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -2549,7 +2551,7 @@
       <c r="D94" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="8">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
@@ -2567,7 +2569,7 @@
       <c r="D95" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="8">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
@@ -2585,7 +2587,7 @@
       <c r="D96" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="8">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
@@ -2603,7 +2605,7 @@
       <c r="D97" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -2621,7 +2623,7 @@
       <c r="D98" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="8">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -2639,7 +2641,7 @@
       <c r="D99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="8">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -2657,7 +2659,7 @@
       <c r="D100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="8">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -2675,7 +2677,7 @@
       <c r="D101" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="8">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -2693,7 +2695,7 @@
       <c r="D102" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -2711,7 +2713,7 @@
       <c r="D103" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="8">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -2729,7 +2731,7 @@
       <c r="D104" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -2747,7 +2749,7 @@
       <c r="D105" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="8">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2765,7 +2767,7 @@
       <c r="D106" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="8">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2783,7 +2785,7 @@
       <c r="D107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="8">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2801,7 +2803,7 @@
       <c r="D108" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="8">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -2819,7 +2821,7 @@
       <c r="D109" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="8">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -2837,7 +2839,7 @@
       <c r="D110" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2855,7 +2857,7 @@
       <c r="D111" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2873,7 +2875,7 @@
       <c r="D112" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2891,7 +2893,7 @@
       <c r="D113" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2909,7 +2911,7 @@
       <c r="D114" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2927,7 +2929,7 @@
       <c r="D115" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2945,7 +2947,7 @@
       <c r="D116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2963,7 +2965,7 @@
       <c r="D117" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="8">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -2981,7 +2983,7 @@
       <c r="D118" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -2999,7 +3001,7 @@
       <c r="D119" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -3017,7 +3019,7 @@
       <c r="D120" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -3035,7 +3037,7 @@
       <c r="D121" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -3053,7 +3055,7 @@
       <c r="D122" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -3071,7 +3073,7 @@
       <c r="D123" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3089,7 +3091,7 @@
       <c r="D124" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3107,7 +3109,7 @@
       <c r="D125" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3125,7 +3127,7 @@
       <c r="D126" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3143,7 +3145,7 @@
       <c r="D127" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3161,7 +3163,7 @@
       <c r="D128" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3179,7 +3181,7 @@
       <c r="D129" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3197,7 +3199,7 @@
       <c r="D130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3215,7 +3217,7 @@
       <c r="D131" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="8">
         <f t="shared" ref="E131:E138" si="2">B131/4</f>
         <v>1</v>
       </c>
@@ -3233,7 +3235,7 @@
       <c r="D132" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E132">
+      <c r="E132" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -3251,7 +3253,7 @@
       <c r="D133" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E133">
+      <c r="E133" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -3269,7 +3271,7 @@
       <c r="D134" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E134">
+      <c r="E134" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -3287,7 +3289,7 @@
       <c r="D135" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E135">
+      <c r="E135" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -3305,7 +3307,7 @@
       <c r="D136" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E136">
+      <c r="E136" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -3323,7 +3325,7 @@
       <c r="D137" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E137">
+      <c r="E137" s="8">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -3341,7 +3343,7 @@
       <c r="D138" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E138">
+      <c r="E138" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>

--- a/MainTop/31.05.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/31.05.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\31.05.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4A5883-BCBE-45E8-82F1-D976E0108EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC22933-FCB3-4C13-BD21-D5BE311F8FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,6 +473,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
